--- a/Reports/ForPopulation/InformationBillBigRSO_Small/InformationBillBigRSO_Small.xlsx
+++ b/Reports/ForPopulation/InformationBillBigRSO_Small/InformationBillBigRSO_Small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\ForPopulation\InformationBillBigRSO_Small\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE079311-4BCA-4A21-8874-EC63EE626071}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEAE2CA-F351-422D-BE2B-B89D151F108A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="60" windowWidth="17100" windowHeight="10110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="95">
   <si>
     <t>ПЛАТЕЖНЫЙ ДОКУМЕНТ</t>
   </si>
@@ -303,7 +303,10 @@
     <t>Итого:</t>
   </si>
   <si>
-    <t>Внимание! С 01.01.2026 изменение нормативов потребления по отоплению в домах с общедомовыми приборами.</t>
+    <t>$this-&gt;H['text1'] = $t1['text1']</t>
+  </si>
+  <si>
+    <t>$SpecData_this-&gt;H['text1']</t>
   </si>
 </sst>
 </file>
@@ -366,20 +369,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
       <charset val="204"/>
-      <scheme val="major"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Cambria"/>
-      <family val="1"/>
+      <sz val="10"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
       <charset val="204"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -700,6 +701,32 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -735,9 +762,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -747,34 +771,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1139,22 +1140,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
       <c r="H1" s="28"/>
       <c r="I1" s="28"/>
-      <c r="J1" s="48" t="s">
+      <c r="J1" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="50"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="60"/>
       <c r="N1" s="30" t="s">
         <v>20</v>
       </c>
@@ -1172,34 +1173,34 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
       <c r="H2" s="28"/>
       <c r="I2" s="28"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="53"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
     </row>
     <row r="3" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56" t="s">
+      <c r="B3" s="65"/>
+      <c r="C3" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
       <c r="I3" s="25"/>
       <c r="J3" s="1" t="s">
         <v>80</v>
@@ -1208,14 +1209,14 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
       <c r="I4" s="33"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1340,6 +1341,9 @@
         <v>27</v>
       </c>
       <c r="G10" s="2"/>
+      <c r="K10" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="O10" s="2"/>
     </row>
@@ -1413,40 +1417,40 @@
       <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="D15" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="43" t="s">
+      <c r="E15" s="54"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="44"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="54" t="s">
+      <c r="H15" s="54"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="K15" s="54" t="s">
+      <c r="K15" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="L15" s="54" t="s">
+      <c r="L15" s="47" t="s">
         <v>17</v>
       </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="18" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="64"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="27" t="s">
         <v>12</v>
       </c>
@@ -1465,9 +1469,9 @@
       <c r="I16" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
+      <c r="J16" s="64"/>
+      <c r="K16" s="64"/>
+      <c r="L16" s="64"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
@@ -1524,14 +1528,14 @@
       <c r="S17" s="13"/>
     </row>
     <row r="18" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="56" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="47"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
       <c r="G18" s="11" t="s">
         <v>57</v>
       </c>
@@ -1595,19 +1599,19 @@
       </c>
     </row>
     <row r="20" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="58" t="s">
+      <c r="C20" s="42"/>
+      <c r="D20" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
       <c r="J20" s="16"/>
@@ -1616,17 +1620,17 @@
       <c r="M20" s="16"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="64"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="58" t="s">
+      <c r="A21" s="48"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="59"/>
-      <c r="F21" s="58" t="s">
+      <c r="E21" s="42"/>
+      <c r="F21" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="59"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
@@ -1644,18 +1648,18 @@
       <c r="A22" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="65" t="s">
+      <c r="B22" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="60" t="s">
+      <c r="C22" s="50"/>
+      <c r="D22" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60" t="s">
+      <c r="E22" s="43"/>
+      <c r="F22" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="61"/>
+      <c r="G22" s="44"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
@@ -1709,38 +1713,38 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="62" t="s">
+      <c r="A24" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="62" t="s">
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="K24" s="62"/>
+      <c r="K24" s="45"/>
     </row>
     <row r="25" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="63"/>
-      <c r="H25" s="63"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
     </row>
     <row r="26" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="68"/>
       <c r="C26" s="68"/>
@@ -1787,15 +1791,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J24:K25"/>
-    <mergeCell ref="A24:I25"/>
-    <mergeCell ref="B20:C21"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="A26:L27"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -1812,6 +1807,15 @@
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="C3:H4"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J24:K25"/>
+    <mergeCell ref="A24:I25"/>
+    <mergeCell ref="B20:C21"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D21:E21"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.31496062992125984" header="0" footer="0"/>
